--- a/data/Evenements_Semaine_Innovation_2026.xlsx
+++ b/data/Evenements_Semaine_Innovation_2026.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evenements" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evenements'!$A$1:$M$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Evenements'!$A$1:$N$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -459,8 +459,9 @@
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="44" customWidth="1" min="10" max="10"/>
     <col width="40" customWidth="1" min="11" max="11"/>
-    <col width="70" customWidth="1" min="12" max="12"/>
-    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="70" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -521,10 +522,15 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>Cibles</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Lien</t>
         </is>
@@ -576,12 +582,17 @@
           <t>Enseignants-chercheurs, doctorants</t>
         </is>
       </c>
-      <c r="L2" s="4" t="inlineStr">
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>Pédagogie, Recherche</t>
+        </is>
+      </c>
+      <c r="M2" s="4" t="inlineStr">
         <is>
           <t>Initiation au Transmedia Storytelling : concevoir en groupe une stratégie de récits multiplateformes pour valoriser un projet.</t>
         </is>
       </c>
-      <c r="M2" s="5" t="inlineStr">
+      <c r="N2" s="5" t="inlineStr">
         <is>
           <t>https://www.u-bordeaux.fr/evenements/le-transmedia-storytelling-comme-valorisation-de-projets</t>
         </is>
@@ -633,12 +644,17 @@
           <t>Personnels</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>Pédagogie, Recherche</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>Jeux de société détournés et défis de créativité pour découvrir les méthodes de l’innovation de façon ludique, sans prérequis.</t>
         </is>
       </c>
-      <c r="M3" s="5" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr">
         <is>
           <t>https://www.u-bordeaux.fr/evenements/les-dejeuxners-de-linnovation</t>
         </is>
@@ -694,12 +710,17 @@
           <t>Enseignants-chercheurs, chercheurs, personnels, étudiants</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>Pédagogie, Étudiants</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>Outils ludiques (jeu de société collaboratif, calculateur Ecobalyse) pour évaluer l’empreinte environnementale de produits.</t>
         </is>
       </c>
-      <c r="M4" s="5" t="inlineStr">
+      <c r="N4" s="5" t="inlineStr">
         <is>
           <t>https://www.u-bordeaux.fr/evenements/evaluer-pour-mieux-maitriser-les-impacts-environnementaux</t>
         </is>
@@ -751,12 +772,17 @@
           <t>Enseignants-chercheurs, accompagnants pédagogiques</t>
         </is>
       </c>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>Pédagogie</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>Atelier de co-conception pour imaginer des espaces d’apprentissage innovants et inclusifs, à partir de scénarios pédagogiques concrets.</t>
         </is>
       </c>
-      <c r="M5" s="5" t="inlineStr">
+      <c r="N5" s="5" t="inlineStr">
         <is>
           <t>https://www.u-bordeaux.fr/evenements/construisons-ensemble-un-espace-pour-apprendre-autrement</t>
         </is>
@@ -804,8 +830,13 @@
           <t>Grand public</t>
         </is>
       </c>
-      <c r="L6" s="4" t="n"/>
-      <c r="M6" s="5" t="inlineStr">
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>Pédagogie, Recherche, Étudiants, Entreprises</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="n"/>
+      <c r="N6" s="5" t="inlineStr">
         <is>
           <t>https://www.u-bordeaux.fr/evenements/semaine-de-linnovation-2026-3e-edition</t>
         </is>
@@ -857,12 +888,17 @@
           <t>Enseignants-chercheurs, chercheurs, doctorants, étudiants de master</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>Recherche</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
         <is>
           <t>Des binômes chercheur / industriel partagent leurs retours sur leurs collaborations ; présentation des dispositifs pour monter et financer des projets communs.</t>
         </is>
       </c>
-      <c r="M7" s="5" t="inlineStr">
+      <c r="N7" s="5" t="inlineStr">
         <is>
           <t>https://www.u-bordeaux.fr/evenements/entractes-regards-croises-sur-les-collaborations-entre-recherche-academique-en-sante-et-entreprise</t>
         </is>
@@ -918,12 +954,17 @@
           <t>Enseignants-chercheurs, acteurs socio-économiques</t>
         </is>
       </c>
-      <c r="L8" s="4" t="inlineStr">
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>Recherche, Entreprises</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
         <is>
           <t>Matinée organisée par NOBATEK et l’université de Bordeaux (équipe GP2E) sur la performance énergétique et environnementale des bâtiments.</t>
         </is>
       </c>
-      <c r="M8" s="5" t="inlineStr">
+      <c r="N8" s="5" t="inlineStr">
         <is>
           <t>https://www.u-bordeaux.fr/evenements/matinale-scientifique-garantie-de-performances-energetiques-et-environnementales-des-batiments</t>
         </is>
@@ -975,12 +1016,17 @@
           <t>Étudiants, personnels, acteurs socio-économiques</t>
         </is>
       </c>
-      <c r="L9" s="4" t="inlineStr">
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>Étudiants, Entreprises</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
         <is>
           <t>Journée de présentations, témoignages et échanges sur les dispositifs d’appui à l’entrepreneuriat agricole et agroalimentaire, avec visite de la plateforme FarmLab@Bordeaux.</t>
         </is>
       </c>
-      <c r="M9" s="5" t="inlineStr">
+      <c r="N9" s="5" t="inlineStr">
         <is>
           <t>https://www.u-bordeaux.fr/evenements/un-terrain-fertile-pour-lentrepreneuriat-et-linnovation-au-service-des-transitions-agroecologiques</t>
         </is>
@@ -1032,12 +1078,17 @@
           <t>Enseignants-chercheurs, ingénieurs, professionnels de la formation</t>
         </is>
       </c>
-      <c r="L10" s="4" t="inlineStr">
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>Pédagogie</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
         <is>
           <t>Visite de la Learning Factory des Arts et Métiers : des plateformes pédagogiques proches de l’industrie, du prototypage à la production mécanique.</t>
         </is>
       </c>
-      <c r="M10" s="5" t="inlineStr">
+      <c r="N10" s="5" t="inlineStr">
         <is>
           <t>https://www.u-bordeaux.fr/evenements/les-evolutive-learning-factories-des-usines-ecoles-pour-apprendre-autrement</t>
         </is>
@@ -1085,12 +1136,17 @@
           <t>Étudiants</t>
         </is>
       </c>
-      <c r="L11" s="4" t="inlineStr">
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>Étudiants</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
         <is>
           <t>Jeux de société détournés et défis de créativité pour découvrir les méthodes de l’innovation de façon ludique, sans prérequis.</t>
         </is>
       </c>
-      <c r="M11" s="5" t="inlineStr">
+      <c r="N11" s="5" t="inlineStr">
         <is>
           <t>https://www.u-bordeaux.fr/evenements/les-dejeuxners-de-linnovation</t>
         </is>
@@ -1138,12 +1194,17 @@
           <t>Acteurs socio-économiques</t>
         </is>
       </c>
-      <c r="L12" s="4" t="inlineStr">
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>Entreprises</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
         <is>
           <t>Visite commentée du CATIE, centre de ressources technologiques du numérique : expertises, équipements et projets menés avec des entreprises.</t>
         </is>
       </c>
-      <c r="M12" s="5" t="inlineStr">
+      <c r="N12" s="5" t="inlineStr">
         <is>
           <t>https://www.u-bordeaux.fr/evenements/de-la-recheche-linnovation-concrete-en-entreprise-la-valeur-ajoutee-dun-centre-de-ressources-technologiques-comme-le-catie</t>
         </is>
@@ -1195,12 +1256,17 @@
           <t>Architectes, ingénieurs, chercheurs, étudiants, professionnels de la construction et de la filière bois</t>
         </is>
       </c>
-      <c r="L13" s="4" t="inlineStr">
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>Recherche, Étudiants, Entreprises</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
         <is>
           <t>Visite des démonstrateurs THRIVE et TNEB : construire avec le hêtre et les feuillus locaux, la terre-paille et le chanvre. Départs des visites à 16 h et 17 h.</t>
         </is>
       </c>
-      <c r="M13" s="5" t="inlineStr">
+      <c r="N13" s="5" t="inlineStr">
         <is>
           <t>https://www.u-bordeaux.fr/evenements/construire-autrement-avec-le-hetre-la-terre-paille-et-le-chanvre</t>
         </is>
@@ -1256,12 +1322,17 @@
           <t>Étudiants et doctorants en sciences humaines et sociales</t>
         </is>
       </c>
-      <c r="L14" s="4" t="inlineStr">
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>Recherche, Étudiants</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
         <is>
           <t>Soirée en trois temps : table ronde, atelier collaboratif et pitchs d’étudiants autour de l’innovation en SHS.</t>
         </is>
       </c>
-      <c r="M14" s="5" t="inlineStr">
+      <c r="N14" s="5" t="inlineStr">
         <is>
           <t>https://www.u-bordeaux.fr/evenements/mardis-de-lentrepreneuriat-les-sciences-humaines-et-sociales-moteur-dinnovation</t>
         </is>
@@ -1317,12 +1388,17 @@
           <t>Chercheurs en sciences humaines et sociales</t>
         </is>
       </c>
-      <c r="L15" s="4" t="inlineStr">
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>Recherche, Entreprises</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="inlineStr">
         <is>
           <t>Transformer une première collaboration avec un acteur socio-économique en partenariat durable : témoignages et échanges avec des experts.</t>
         </is>
       </c>
-      <c r="M15" s="5" t="inlineStr">
+      <c r="N15" s="5" t="inlineStr">
         <is>
           <t>https://www.u-bordeaux.fr/evenements/faire-grandir-ses-partenariats-construire-des-collaborations-structurantes-en-sciences-humaines-et-sociales</t>
         </is>
@@ -1374,12 +1450,17 @@
           <t>Chercheurs du numérique, personnels de la valorisation, acteurs socio-économiques</t>
         </is>
       </c>
-      <c r="L16" s="4" t="inlineStr">
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>Recherche, Entreprises</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="inlineStr">
         <is>
           <t>Valoriser les logiciels de recherche en Open Source : visibilité, collaborations avec les entreprises, modèles économiques, licences.</t>
         </is>
       </c>
-      <c r="M16" s="5" t="inlineStr">
+      <c r="N16" s="5" t="inlineStr">
         <is>
           <t>https://www.u-bordeaux.fr/evenements/du-laboratoire-lentreprise-le-potentiel-de-lopen-source-issu-de-la-recherche</t>
         </is>
@@ -1431,12 +1512,17 @@
           <t>Chercheurs, enseignants-chercheurs, industriels</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>Recherche, Entreprises</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
         <is>
           <t>Journée autour des équipements de micro et nanofabrication du site bordelais pour définir une feuille de route technologique en photonique.</t>
         </is>
       </c>
-      <c r="M17" s="5" t="inlineStr">
+      <c r="N17" s="5" t="inlineStr">
         <is>
           <t>https://www.u-bordeaux.fr/evenements/micro-et-nanofabrication-pour-la-photonique-avancee</t>
         </is>
@@ -1488,12 +1574,17 @@
           <t>Acteurs socio-économiques du secteur spatial</t>
         </is>
       </c>
-      <c r="L18" s="4" t="inlineStr">
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>Entreprises</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="inlineStr">
         <is>
           <t>Découvrir les expertises, laboratoires et plateformes spatiales de l’université de Bordeaux, puis échanger avec les chercheurs (avec Aerospace Valley).</t>
         </is>
       </c>
-      <c r="M18" s="5" t="inlineStr">
+      <c r="N18" s="5" t="inlineStr">
         <is>
           <t>https://www.u-bordeaux.fr/evenements/explorer-lespace-avec-nos-experts</t>
         </is>
@@ -1545,12 +1636,17 @@
           <t>Enseignants-chercheurs, chercheurs, acteurs socio-économiques</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>Recherche, Entreprises</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>Les coulisses des collaborations laboratoires-entreprises et le rôle des cellules de transfert technologique.</t>
         </is>
       </c>
-      <c r="M19" s="5" t="inlineStr">
+      <c r="N19" s="5" t="inlineStr">
         <is>
           <t>https://www.u-bordeaux.fr/evenements/les-cellules-de-transfert-technologique-en-pratique</t>
         </is>
@@ -1610,12 +1706,17 @@
           <t>Acteurs socio-économiques (start-ups, deeptech, PME, ETI)</t>
         </is>
       </c>
-      <c r="L20" s="4" t="inlineStr">
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>Entreprises</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
         <is>
           <t>Rencontrer les plateformes technologiques de l’université de Bordeaux et découvrir leurs équipements et compétences.</t>
         </is>
       </c>
-      <c r="M20" s="5" t="inlineStr">
+      <c r="N20" s="5" t="inlineStr">
         <is>
           <t>https://www.u-bordeaux.fr/evenements/salon-des-entreprises-du-concept-au-demonstrateur</t>
         </is>
@@ -1667,12 +1768,17 @@
           <t>Enseignants-chercheurs, chercheurs, acteurs socio-économiques</t>
         </is>
       </c>
-      <c r="L21" s="4" t="inlineStr">
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>Recherche</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
         <is>
           <t>Rencontres entre chercheurs du GIS Albatros et industriels pour identifier des sujets communs (micro-projets, études, thèses CIFRE).</t>
         </is>
       </c>
-      <c r="M21" s="5" t="inlineStr">
+      <c r="N21" s="5" t="inlineStr">
         <is>
           <t>https://www.u-bordeaux.fr/evenements/albatros-techno-day-2026</t>
         </is>
@@ -1728,12 +1834,17 @@
           <t>Enseignants-chercheurs</t>
         </is>
       </c>
-      <c r="L22" s="4" t="inlineStr">
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>Pédagogie</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
         <is>
           <t>Présentation de la plateforme CampusIABordeaux et de son usage avec les étudiants : publication, partage et réutilisation des données.</t>
         </is>
       </c>
-      <c r="M22" s="5" t="inlineStr">
+      <c r="N22" s="5" t="inlineStr">
         <is>
           <t>https://www.u-bordeaux.fr/evenements/campusiabordeaux-entrainez-vos-etudiants-sur-la-donnee</t>
         </is>
@@ -1789,12 +1900,17 @@
           <t>Enseignants-chercheurs</t>
         </is>
       </c>
-      <c r="L23" s="4" t="inlineStr">
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>Pédagogie</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
         <is>
           <t>Présentation du dispositif qui accompagne des projets d’acteurs de la société et co-construit des questions de recherche. Accueil café à 10 h 30, atelier à 10 h 45.</t>
         </is>
       </c>
-      <c r="M23" s="5" t="inlineStr">
+      <c r="N23" s="5" t="inlineStr">
         <is>
           <t>https://www.u-bordeaux.fr/evenements/echoppe-des-sciences-decouvrez-questionnez-adoptez</t>
         </is>
@@ -1842,12 +1958,17 @@
           <t>Étudiants</t>
         </is>
       </c>
-      <c r="L24" s="4" t="inlineStr">
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>Étudiants</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
         <is>
           <t>Jeux de société détournés et défis de créativité pour découvrir les méthodes de l’innovation de façon ludique, sans prérequis.</t>
         </is>
       </c>
-      <c r="M24" s="5" t="inlineStr">
+      <c r="N24" s="5" t="inlineStr">
         <is>
           <t>https://www.u-bordeaux.fr/evenements/les-dejeuxners-de-linnovation</t>
         </is>
@@ -1903,12 +2024,17 @@
           <t>Chercheurs, enseignants-chercheurs, doctorants</t>
         </is>
       </c>
-      <c r="L25" s="4" t="inlineStr">
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>Pédagogie, Recherche</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
         <is>
           <t>Visite du FabLabNab (impression 3D, découpe laser, prototypage rapide) et temps d’échange sur la science ouverte et l’innovation frugale.</t>
         </is>
       </c>
-      <c r="M25" s="5" t="inlineStr">
+      <c r="N25" s="5" t="inlineStr">
         <is>
           <t>https://www.u-bordeaux.fr/evenements/pepiniere-numerique-fablabnab-quand-la-fabrication-numerique-booste-linnovation</t>
         </is>
@@ -1960,12 +2086,17 @@
           <t>Enseignants-chercheurs, chercheurs, ingénieurs, doctorants, acteurs socio-économiques</t>
         </is>
       </c>
-      <c r="L26" s="4" t="inlineStr">
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>Pédagogie, Recherche, Entreprises</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
         <is>
           <t>Présentation-visite d’une cellule robotisée de fabrication additive métallique (WAAM) : fonctionnement, usages industriels et défis.</t>
         </is>
       </c>
-      <c r="M26" s="5" t="inlineStr">
+      <c r="N26" s="5" t="inlineStr">
         <is>
           <t>https://www.u-bordeaux.fr/evenements/la-robotique-au-service-de-la-fabrication-additive-metallique</t>
         </is>
@@ -2017,12 +2148,17 @@
           <t>Docteurs et doctorants</t>
         </is>
       </c>
-      <c r="L27" s="4" t="inlineStr">
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>Recherche, Entreprises</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr">
         <is>
           <t>Soirée de rencontre entre docteurs, doctorants et entreprises bordelaises : témoignages, échanges en petits groupes et réseautage.</t>
         </is>
       </c>
-      <c r="M27" s="5" t="inlineStr">
+      <c r="N27" s="5" t="inlineStr">
         <is>
           <t>https://www.u-bordeaux.fr/evenements/afterwork-docteurs-doctorants-et-entreprises</t>
         </is>
@@ -2078,12 +2214,17 @@
           <t>Enseignants-chercheurs</t>
         </is>
       </c>
-      <c r="L28" s="4" t="inlineStr">
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>Pédagogie</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
         <is>
           <t>Présentation de la plateforme CampusIABordeaux et de son usage avec les étudiants : publication, partage et réutilisation des données.</t>
         </is>
       </c>
-      <c r="M28" s="5" t="inlineStr">
+      <c r="N28" s="5" t="inlineStr">
         <is>
           <t>https://www.u-bordeaux.fr/evenements/campusiabordeaux-entrainez-vos-etudiants-sur-la-donnee</t>
         </is>
@@ -2135,12 +2276,17 @@
           <t>Accompagnants à l’innovation, enseignants-chercheurs</t>
         </is>
       </c>
-      <c r="L29" s="4" t="inlineStr">
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>Pédagogie, Recherche</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
         <is>
           <t>Trois retours d’expérience sur des formations-accompagnements conçus sur mesure pour répondre à des besoins collectifs.</t>
         </is>
       </c>
-      <c r="M29" s="5" t="inlineStr">
+      <c r="N29" s="5" t="inlineStr">
         <is>
           <t>https://www.u-bordeaux.fr/evenements/des-formations-sur-mesure-pour-faire-evoluer-ses-pratiques</t>
         </is>
@@ -2192,12 +2338,13 @@
           <t>Personnels administratifs</t>
         </is>
       </c>
-      <c r="L30" s="4" t="inlineStr">
+      <c r="L30" s="5" t="n"/>
+      <c r="M30" s="4" t="inlineStr">
         <is>
           <t>Jeu en équipes de 4 à 5 personnes pour tester sa connaissance de l’écosystème d’innovation bordelais et savoir orienter les porteurs de projets.</t>
         </is>
       </c>
-      <c r="M30" s="5" t="inlineStr">
+      <c r="N30" s="5" t="inlineStr">
         <is>
           <t>https://www.u-bordeaux.fr/evenements/le-pole-universitaire-dinnovation-bordeaux-en-jeu-venez-relever-le-defi</t>
         </is>
@@ -2253,19 +2400,24 @@
           <t>Enseignants-chercheurs</t>
         </is>
       </c>
-      <c r="L31" s="4" t="inlineStr">
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>Pédagogie</t>
+        </is>
+      </c>
+      <c r="M31" s="4" t="inlineStr">
         <is>
           <t>Présentation de la plateforme CampusIABordeaux et de son usage avec les étudiants : publication, partage et réutilisation des données.</t>
         </is>
       </c>
-      <c r="M31" s="5" t="inlineStr">
+      <c r="N31" s="5" t="inlineStr">
         <is>
           <t>https://www.u-bordeaux.fr/evenements/campusiabordeaux-entrainez-vos-etudiants-sur-la-donnee</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M31"/>
+  <autoFilter ref="A1:N31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/Evenements_Semaine_Innovation_2026.xlsx
+++ b/data/Evenements_Semaine_Innovation_2026.xlsx
@@ -2338,7 +2338,11 @@
           <t>Personnels administratifs</t>
         </is>
       </c>
-      <c r="L30" s="5" t="n"/>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>Personnels</t>
+        </is>
+      </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
           <t>Jeu en équipes de 4 à 5 personnes pour tester sa connaissance de l’écosystème d’innovation bordelais et savoir orienter les porteurs de projets.</t>

--- a/data/Evenements_Semaine_Innovation_2026.xlsx
+++ b/data/Evenements_Semaine_Innovation_2026.xlsx
@@ -890,7 +890,7 @@
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>Recherche</t>
+          <t>Recherche, Entreprises</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>Pédagogie</t>
+          <t>Pédagogie, Entreprises</t>
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Construire autrement avec le hêtre, la terre-paille et le chanvre</t>
+          <t>Construire autrement : bois de feuillus, et terres allégées</t>
         </is>
       </c>
       <c r="E13" s="4" t="n"/>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Explorer l’Espace avec nos experts</t>
+          <t>Space Meet-Up Nouvelle-Aquitaine : explorer l’Espace avec nos experts</t>
         </is>
       </c>
       <c r="E18" s="4" t="n"/>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Soirée des entreprises</t>
+          <t>Salon des entreprises</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>L’Échoppe des Sciences</t>
+          <t>Échoppe des Sciences</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Serious game « No wrong door » avec le Pôle universitaire d’innovation Bordeaux</t>
+          <t>Serious Game « No wrong door » du Pôle universitaire d’innovation Bordeaux</t>
         </is>
       </c>
       <c r="E30" s="4" t="n"/>
